--- a/artfynd/A 23553-2024 artfynd.xlsx
+++ b/artfynd/A 23553-2024 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120495619</v>
+        <v>120496101</v>
       </c>
       <c r="B5" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1037,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628329</v>
+        <v>628383</v>
       </c>
       <c r="R5" t="n">
-        <v>6898656</v>
+        <v>6898650</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120496101</v>
+        <v>120495619</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,47 +1158,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628383</v>
+        <v>628329</v>
       </c>
       <c r="R6" t="n">
-        <v>6898650</v>
+        <v>6898656</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 23553-2024 artfynd.xlsx
+++ b/artfynd/A 23553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120495529</v>
+        <v>120496000</v>
       </c>
       <c r="B2" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628269</v>
+        <v>628393</v>
       </c>
       <c r="R2" t="n">
-        <v>6898665</v>
+        <v>6898644</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ganska rikligt på en murken tallåga</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120496222</v>
+        <v>120496456</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628373</v>
+        <v>628235</v>
       </c>
       <c r="R3" t="n">
-        <v>6898646</v>
+        <v>6898650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1025,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120496101</v>
+        <v>120496637</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1060,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1074,7 +1069,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628383</v>
+        <v>628235</v>
       </c>
       <c r="R5" t="n">
         <v>6898650</v>
@@ -1109,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120495619</v>
+        <v>120495682</v>
       </c>
       <c r="B6" t="n">
-        <v>74593</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,21 +1157,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628329</v>
+        <v>628316</v>
       </c>
       <c r="R6" t="n">
-        <v>6898656</v>
+        <v>6898678</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120495682</v>
+        <v>120495619</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
+        <v>74593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628316</v>
+        <v>628329</v>
       </c>
       <c r="R7" t="n">
-        <v>6898678</v>
+        <v>6898656</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120495944</v>
+        <v>120496101</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1405,12 +1400,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628414</v>
+        <v>628383</v>
       </c>
       <c r="R8" t="n">
-        <v>6898651</v>
+        <v>6898650</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120496637</v>
+        <v>120495644</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,47 +1498,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628235</v>
+        <v>628329</v>
       </c>
       <c r="R9" t="n">
-        <v>6898650</v>
+        <v>6898656</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1575,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1585,7 +1571,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Förekommer mycket frekvent i beståndet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120496456</v>
+        <v>120496222</v>
       </c>
       <c r="B10" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,38 +1615,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628235</v>
+        <v>628373</v>
       </c>
       <c r="R10" t="n">
-        <v>6898650</v>
+        <v>6898646</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,7 +1724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120496000</v>
+        <v>120495944</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628393</v>
+        <v>628414</v>
       </c>
       <c r="R11" t="n">
-        <v>6898644</v>
+        <v>6898651</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,14 +1845,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120495644</v>
+        <v>120495529</v>
       </c>
       <c r="B12" t="n">
         <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628329</v>
+        <v>628269</v>
       </c>
       <c r="R12" t="n">
-        <v>6898656</v>
+        <v>6898665</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förekommer mycket frekvent i beståndet</t>
+          <t>Ganska rikligt på en murken tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 23553-2024 artfynd.xlsx
+++ b/artfynd/A 23553-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120496000</v>
+        <v>120495644</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628393</v>
+        <v>628329</v>
       </c>
       <c r="R2" t="n">
-        <v>6898644</v>
+        <v>6898656</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Förekommer mycket frekvent i beståndet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120496155</v>
+        <v>120496101</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628380</v>
+        <v>628383</v>
       </c>
       <c r="R4" t="n">
-        <v>6898638</v>
+        <v>6898650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120496637</v>
+        <v>120495682</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1037,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628235</v>
+        <v>628316</v>
       </c>
       <c r="R5" t="n">
-        <v>6898650</v>
+        <v>6898678</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120495682</v>
+        <v>120496155</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628316</v>
+        <v>628380</v>
       </c>
       <c r="R6" t="n">
-        <v>6898678</v>
+        <v>6898638</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120495619</v>
+        <v>120496000</v>
       </c>
       <c r="B7" t="n">
-        <v>74593</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1261,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628329</v>
+        <v>628393</v>
       </c>
       <c r="R7" t="n">
-        <v>6898656</v>
+        <v>6898644</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120496101</v>
+        <v>120495944</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1400,12 +1405,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628383</v>
+        <v>628414</v>
       </c>
       <c r="R8" t="n">
-        <v>6898650</v>
+        <v>6898651</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120495644</v>
+        <v>120496637</v>
       </c>
       <c r="B9" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,38 +1503,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628329</v>
+        <v>628235</v>
       </c>
       <c r="R9" t="n">
-        <v>6898656</v>
+        <v>6898650</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,12 +1585,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Förekommer mycket frekvent i beståndet</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120496222</v>
+        <v>120495619</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,47 +1624,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628373</v>
+        <v>628329</v>
       </c>
       <c r="R10" t="n">
-        <v>6898646</v>
+        <v>6898656</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,7 +1724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120495944</v>
+        <v>120496222</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628414</v>
+        <v>628373</v>
       </c>
       <c r="R11" t="n">
-        <v>6898651</v>
+        <v>6898646</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 23553-2024 artfynd.xlsx
+++ b/artfynd/A 23553-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120496155</v>
+        <v>120495529</v>
       </c>
       <c r="B2" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628380</v>
+        <v>628269</v>
       </c>
       <c r="R2" t="n">
-        <v>6898638</v>
+        <v>6898665</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ganska rikligt på en murken tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +790,7 @@
         <v>120495644</v>
       </c>
       <c r="B3" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,37 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120496456</v>
+        <v>120495819</v>
       </c>
       <c r="B4" t="n">
-        <v>90450</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628235</v>
+        <v>628382</v>
       </c>
       <c r="R4" t="n">
-        <v>6898650</v>
+        <v>6898688</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120495682</v>
+        <v>120496155</v>
       </c>
       <c r="B5" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628316</v>
+        <v>628380</v>
       </c>
       <c r="R5" t="n">
-        <v>6898678</v>
+        <v>6898638</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,59 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120496000</v>
+        <v>120496456</v>
       </c>
       <c r="B6" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628393</v>
+        <v>628235</v>
       </c>
       <c r="R6" t="n">
-        <v>6898644</v>
+        <v>6898650</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,59 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120496101</v>
+        <v>120495682</v>
       </c>
       <c r="B7" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628383</v>
+        <v>628316</v>
       </c>
       <c r="R7" t="n">
-        <v>6898650</v>
+        <v>6898678</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,59 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120496637</v>
+        <v>120495831</v>
       </c>
       <c r="B8" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628235</v>
+        <v>628380</v>
       </c>
       <c r="R8" t="n">
-        <v>6898650</v>
+        <v>6898683</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,16 +1437,11 @@
         <v>120495619</v>
       </c>
       <c r="B9" t="n">
-        <v>74641</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1606,12 +1544,7 @@
         <v>120495944</v>
       </c>
       <c r="B10" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,15 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120496222</v>
+        <v>120496000</v>
       </c>
       <c r="B11" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1687,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1773,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628373</v>
+        <v>628393</v>
       </c>
       <c r="R11" t="n">
-        <v>6898646</v>
+        <v>6898644</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1808,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1746,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,50 +1773,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120495529</v>
+        <v>120496101</v>
       </c>
       <c r="B12" t="n">
-        <v>95601</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628269</v>
+        <v>628383</v>
       </c>
       <c r="R12" t="n">
-        <v>6898665</v>
+        <v>6898650</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,12 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ganska rikligt på en murken tallåga</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,6 +1886,238 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120496222</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Getryggen, Getryggen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>628373</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6898646</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120496637</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Getryggen, Getryggen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>628235</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6898650</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23553-2024 artfynd.xlsx
+++ b/artfynd/A 23553-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495644</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496155</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496456</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495682</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495831</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495619</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120495944</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,6 +1820,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1886,6 +1941,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496101</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2002,6 +2062,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496222</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2118,8 +2183,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>